--- a/02_论文/files/问题一结果.xlsx
+++ b/02_论文/files/问题一结果.xlsx
@@ -477,19 +477,19 @@
         <v>0.719935764230188</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9123300859598855</v>
+        <v>0.912385100286533</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9452642007817726</v>
+        <v>0.9452460360864088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5379975504571782</v>
+        <v>0.5380211328666478</v>
       </c>
       <c r="F2" t="n">
-        <v>29.46297325098455</v>
+        <v>29.46421468502531</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4690062599647334</v>
+        <v>0.4690260217291516</v>
       </c>
     </row>
     <row r="3">
@@ -502,19 +502,19 @@
         <v>0.7404403532037784</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9310406876790831</v>
+        <v>0.9310624641833811</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9391372174150682</v>
+        <v>0.939129805376744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5650671227056366</v>
+        <v>0.5650769539516517</v>
       </c>
       <c r="F3" t="n">
-        <v>33.47288489942572</v>
+        <v>33.47344141409458</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5328380276890438</v>
+        <v>0.532846886566294</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>0.7611400153929363</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9347415472779369</v>
+        <v>0.9347438395415473</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9369602824119667</v>
+        <v>0.9369595126056405</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5843339747888316</v>
+        <v>0.5843350938847023</v>
       </c>
       <c r="F4" t="n">
-        <v>36.51648509181008</v>
+        <v>36.51655221732777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5812875691150919</v>
+        <v>0.5812886376524636</v>
       </c>
     </row>
     <row r="5">
@@ -677,19 +677,19 @@
         <v>0.7600919805120643</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9346750716332378</v>
+        <v>0.9346796561604584</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9370204203081569</v>
+        <v>0.9370190186971227</v>
       </c>
       <c r="E10" t="n">
-        <v>0.583407524250209</v>
+        <v>0.5834098453484813</v>
       </c>
       <c r="F10" t="n">
-        <v>36.37594858921602</v>
+        <v>36.37608738858062</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5790504391788606</v>
+        <v>0.5790526486561705</v>
       </c>
     </row>
     <row r="11">
@@ -702,19 +702,19 @@
         <v>0.7378354064925949</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9296000000000001</v>
+        <v>0.929621776504298</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9397907806195869</v>
+        <v>0.9397834470978808</v>
       </c>
       <c r="E11" t="n">
-        <v>0.562297258475335</v>
+        <v>0.5623069198508632</v>
       </c>
       <c r="F11" t="n">
-        <v>33.03413401362482</v>
+        <v>33.03467513706752</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5258537729007454</v>
+        <v>0.5258623867728035</v>
       </c>
     </row>
     <row r="12">
@@ -727,19 +727,19 @@
         <v>0.7181956127447962</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9104756446991404</v>
+        <v>0.9105444126074499</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9454492280415646</v>
+        <v>0.9454271485134585</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5354139881704807</v>
+        <v>0.5354448199154254</v>
       </c>
       <c r="F12" t="n">
-        <v>29.07488141873674</v>
+        <v>29.07647148486951</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4628284211833292</v>
+        <v>0.4628537326467608</v>
       </c>
     </row>
     <row r="13">
@@ -752,19 +752,19 @@
         <v>0.7110822833457547</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8982166189111748</v>
+        <v>0.8987232091690543</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9468041146246546</v>
+        <v>0.9466433527331709</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5218120216309389</v>
+        <v>0.5220391797486796</v>
       </c>
       <c r="F13" t="n">
-        <v>27.28092793538372</v>
+        <v>27.29159783106129</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4342713775132715</v>
+        <v>0.4344412262187406</v>
       </c>
     </row>
   </sheetData>
@@ -818,19 +818,19 @@
         <v>0.7564654978846909</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9277430754536772</v>
+        <v>0.9277998089780324</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9399649241296042</v>
+        <v>0.9399467638719088</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5776394046103721</v>
+        <v>0.5776647800343589</v>
       </c>
       <c r="E2" t="n">
-        <v>35.31612851053886</v>
+        <v>35.31736225710927</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5621796961244646</v>
+        <v>0.5621993355159068</v>
       </c>
     </row>
   </sheetData>
@@ -908,19 +908,19 @@
         <v>0.7024362414633658</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8826189111747852</v>
+        <v>0.8827277936962752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9529376704693492</v>
+        <v>0.9529011356086364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5069413105683485</v>
+        <v>0.5069844229021282</v>
       </c>
       <c r="H2" t="n">
-        <v>25.23926088932015</v>
+        <v>25.2414073378678</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4017711061655547</v>
+        <v>0.4018052744009519</v>
       </c>
     </row>
     <row r="3">
@@ -937,19 +937,19 @@
         <v>0.7285806317918258</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9298739255014328</v>
+        <v>0.9298968481375358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9407524899963301</v>
+        <v>0.9407448676025318</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5543559812976676</v>
+        <v>0.5543654245442579</v>
       </c>
       <c r="H3" t="n">
-        <v>31.69359900701908</v>
+        <v>31.69413889561207</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5045144700257734</v>
+        <v>0.5045230642408799</v>
       </c>
     </row>
     <row r="4">
@@ -966,19 +966,19 @@
         <v>0.7376450687803956</v>
       </c>
       <c r="E4" t="n">
-        <v>0.933404011461318</v>
+        <v>0.9334269340974213</v>
       </c>
       <c r="F4" t="n">
-        <v>0.938730550156071</v>
+        <v>0.9387235516389887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5634049807861073</v>
+        <v>0.5634156360627355</v>
       </c>
       <c r="H4" t="n">
-        <v>33.24063535344566</v>
+        <v>33.24126400987766</v>
       </c>
       <c r="I4" t="n">
-        <v>0.529140963919861</v>
+        <v>0.5291509711855724</v>
       </c>
     </row>
     <row r="5">
@@ -995,19 +995,19 @@
         <v>0.7285806332659797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.931054441260745</v>
+        <v>0.9311060171919769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9405443167825146</v>
+        <v>0.9405277850589597</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5557033609519854</v>
+        <v>0.5557262125756318</v>
       </c>
       <c r="H5" t="n">
-        <v>31.77063129658545</v>
+        <v>31.77193776791604</v>
       </c>
       <c r="I5" t="n">
-        <v>0.505740708318775</v>
+        <v>0.5057615053791156</v>
       </c>
     </row>
     <row r="6">
@@ -1024,19 +1024,19 @@
         <v>0.7024362458493735</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8846991404011461</v>
+        <v>0.8847679083094556</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9533559765045984</v>
+        <v>0.9533328405229267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5095821186817825</v>
+        <v>0.5096139682484851</v>
       </c>
       <c r="H6" t="n">
-        <v>25.37073970855243</v>
+        <v>25.37232541385295</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4038640513937032</v>
+        <v>0.4038892934392384</v>
       </c>
     </row>
     <row r="7">
@@ -1053,19 +1053,19 @@
         <v>0.7224441368523336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9227163323782234</v>
+        <v>0.9227621776504297</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9421618671038421</v>
+        <v>0.9421457032221076</v>
       </c>
       <c r="G7" t="n">
-        <v>0.545918186865093</v>
+        <v>0.5459386979987289</v>
       </c>
       <c r="H7" t="n">
-        <v>30.43889022534539</v>
+        <v>30.44003386950336</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4845413916801239</v>
+        <v>0.4845595967765577</v>
       </c>
     </row>
     <row r="8">
@@ -1082,19 +1082,19 @@
         <v>0.7493379441013761</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9336045845272205</v>
+        <v>0.933621776504298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9376381620818429</v>
+        <v>0.9376331265003834</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5728244828090552</v>
+        <v>0.5728324694906608</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9340781887593</v>
+        <v>34.93456526179486</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5560980291111001</v>
+        <v>0.5561057825818984</v>
       </c>
     </row>
     <row r="9">
@@ -1169,19 +1169,19 @@
         <v>0.7224441426163722</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9252206303724928</v>
+        <v>0.9252664756446991</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9424454848133768</v>
+        <v>0.9424296240849493</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5486962750544011</v>
+        <v>0.5487169334692348</v>
       </c>
       <c r="H11" t="n">
-        <v>30.59378874945624</v>
+        <v>30.594940605607</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4870071434170047</v>
+        <v>0.4870254792360236</v>
       </c>
     </row>
     <row r="12">
@@ -1198,19 +1198,19 @@
         <v>0.7431561030139224</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9297478510028653</v>
+        <v>0.9297593123209168</v>
       </c>
       <c r="F12" t="n">
-        <v>0.939100964587289</v>
+        <v>0.9390971155556584</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5665800848336736</v>
+        <v>0.5665856803130265</v>
       </c>
       <c r="H12" t="n">
-        <v>33.98456067007867</v>
+        <v>33.98489629766713</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5409831370595141</v>
+        <v>0.5409884797463727</v>
       </c>
     </row>
     <row r="13">
@@ -2068,19 +2068,19 @@
         <v>0.7420918544863451</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9295587392550143</v>
+        <v>0.9295702005730658</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9392496572989646</v>
+        <v>0.9392457770305461</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5656278573932594</v>
+        <v>0.5656334267670461</v>
       </c>
       <c r="H42" t="n">
-        <v>33.82398244075482</v>
+        <v>33.82431548375951</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5384269729505701</v>
+        <v>0.5384322744947392</v>
       </c>
     </row>
     <row r="43">
@@ -2184,19 +2184,19 @@
         <v>0.7420918610912809</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9311002865329513</v>
+        <v>0.9311117478510028</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9390250797611512</v>
+        <v>0.9390219519743989</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5675695176484341</v>
+        <v>0.5675755537660092</v>
       </c>
       <c r="H46" t="n">
-        <v>33.94009178989403</v>
+        <v>33.94045274371235</v>
       </c>
       <c r="I46" t="n">
-        <v>0.540275259310634</v>
+        <v>0.5402810051530141</v>
       </c>
     </row>
     <row r="47">
@@ -2213,19 +2213,19 @@
         <v>0.719877277873434</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9201318051575932</v>
+        <v>0.9201776504297995</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9435001932767942</v>
+        <v>0.943484666876662</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5427378956436325</v>
+        <v>0.5427577438074974</v>
       </c>
       <c r="H47" t="n">
-        <v>29.91363828364345</v>
+        <v>29.91473223856942</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4761801700675494</v>
+        <v>0.476197584186078</v>
       </c>
     </row>
     <row r="48">
@@ -2242,19 +2242,19 @@
         <v>0.7467134392688765</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9330773638968481</v>
+        <v>0.9330945558739255</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9380574376889642</v>
+        <v>0.9380522944202275</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5705189314531153</v>
+        <v>0.5705268371375017</v>
       </c>
       <c r="H48" t="n">
-        <v>34.55709409074452</v>
+        <v>34.55757294861257</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5500970087670252</v>
+        <v>0.5501046314647018</v>
       </c>
     </row>
     <row r="49">
@@ -2329,19 +2329,19 @@
         <v>0.7198772834890129</v>
       </c>
       <c r="E51" t="n">
-        <v>0.921839541547278</v>
+        <v>0.9218853868194843</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9433602653714599</v>
+        <v>0.9433442674317981</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5450047277065301</v>
+        <v>0.5450252807359198</v>
       </c>
       <c r="H51" t="n">
-        <v>30.03857740236644</v>
+        <v>30.03971020678591</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4781690130908379</v>
+        <v>0.4781870456349237</v>
       </c>
     </row>
     <row r="52">
@@ -2358,19 +2358,19 @@
         <v>0.7007578214209315</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8795186246418338</v>
+        <v>0.8796733524355302</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9538231379110388</v>
+        <v>0.9537757092237712</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5036210597549027</v>
+        <v>0.5036880281028238</v>
       </c>
       <c r="H52" t="n">
-        <v>24.76133963557066</v>
+        <v>24.76463224213584</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3941633179810676</v>
+        <v>0.394215731329765</v>
       </c>
     </row>
     <row r="53">
@@ -2387,19 +2387,19 @@
         <v>0.7268092016288019</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9290544412607449</v>
+        <v>0.9290773638968481</v>
       </c>
       <c r="F53" t="n">
-        <v>0.941016434968758</v>
+        <v>0.9410087741354064</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5524221644699435</v>
+        <v>0.5524315779585903</v>
       </c>
       <c r="H53" t="n">
-        <v>31.36631836812453</v>
+        <v>31.36685286239511</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4993046540611992</v>
+        <v>0.499313162406799</v>
       </c>
     </row>
     <row r="54">
@@ -2416,19 +2416,19 @@
         <v>0.7358440119692825</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9327507163323783</v>
+        <v>0.9327736389684814</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9390059911689208</v>
+        <v>0.9389989340615149</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5615801675096054</v>
+        <v>0.5615907813887565</v>
       </c>
       <c r="H54" t="n">
-        <v>32.9415174891472</v>
+        <v>32.9421400846481</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5243794570064821</v>
+        <v>0.5243893677912783</v>
       </c>
     </row>
     <row r="55">
@@ -2445,19 +2445,19 @@
         <v>0.726809203036237</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9302292263610316</v>
+        <v>0.9302865329512894</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9408265105792528</v>
+        <v>0.940808346480506</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5537677107448946</v>
+        <v>0.5537937788848363</v>
       </c>
       <c r="H55" t="n">
-        <v>31.44271796892559</v>
+        <v>31.44419810790129</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5005208208998024</v>
+        <v>0.5005443824880818</v>
       </c>
     </row>
     <row r="56">
@@ -2474,19 +2474,19 @@
         <v>0.7007578256687279</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8808252148997134</v>
+        <v>0.8809111747851003</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9525740655798525</v>
+        <v>0.9525439786660943</v>
       </c>
       <c r="G56" t="n">
-        <v>0.505678838373057</v>
+        <v>0.5057199332421201</v>
       </c>
       <c r="H56" t="n">
-        <v>24.86251363191572</v>
+        <v>24.86453412726721</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3957738559680949</v>
+        <v>0.3958060192178798</v>
       </c>
     </row>
     <row r="57">
@@ -2503,19 +2503,19 @@
         <v>0.693926729281709</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8559828080229227</v>
+        <v>0.8571404011461319</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9535248036331372</v>
+        <v>0.953123412163306</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4815238203396476</v>
+        <v>0.482028255964304</v>
       </c>
       <c r="H57" t="n">
-        <v>22.34280614985332</v>
+        <v>22.36621206852382</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3556638992335772</v>
+        <v>0.3560364862865937</v>
       </c>
     </row>
     <row r="58">
@@ -2532,19 +2532,19 @@
         <v>0.7195529827960064</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9219484240687679</v>
+        <v>0.9220057306590258</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9434640019706531</v>
+        <v>0.9434448596028387</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5432486460454782</v>
+        <v>0.5432744088135439</v>
       </c>
       <c r="H58" t="n">
-        <v>29.89657632821121</v>
+        <v>29.89799412937374</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4759085693761733</v>
+        <v>0.4759311386401422</v>
       </c>
     </row>
     <row r="59">
@@ -2561,19 +2561,19 @@
         <v>0.7284519877952695</v>
       </c>
       <c r="E59" t="n">
-        <v>0.930595988538682</v>
+        <v>0.9306361031518625</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9396315479987687</v>
+        <v>0.939619171446665</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5543689993256853</v>
+        <v>0.5543880668780536</v>
       </c>
       <c r="H59" t="n">
-        <v>31.67878048806821</v>
+        <v>31.67987008147379</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5042785814719549</v>
+        <v>0.504295926161633</v>
       </c>
     </row>
     <row r="60">
@@ -2590,19 +2590,19 @@
         <v>0.7195529839240626</v>
       </c>
       <c r="E60" t="n">
-        <v>0.922865329512894</v>
+        <v>0.9229226361031518</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9430981116680665</v>
+        <v>0.9430794155150174</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5442113280671936</v>
+        <v>0.544236962889087</v>
       </c>
       <c r="H60" t="n">
-        <v>29.94955556111224</v>
+        <v>29.95096632101927</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4767519191517389</v>
+        <v>0.4767743763295013</v>
       </c>
     </row>
     <row r="61">
@@ -2619,19 +2619,19 @@
         <v>0.6939267329317259</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8596905444126075</v>
+        <v>0.8609111747851003</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9543021078526482</v>
+        <v>0.9539499049380272</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4857073143766895</v>
+        <v>0.4862682041984097</v>
       </c>
       <c r="H61" t="n">
-        <v>22.5369211496736</v>
+        <v>22.56294655491582</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3587539183329131</v>
+        <v>0.3591682036758329</v>
       </c>
     </row>
   </sheetData>
